--- a/colegios/EXTRAIDOS CON PYTHON/DEPARTAMENTO_Tarija.xlsx
+++ b/colegios/EXTRAIDOS CON PYTHON/DEPARTAMENTO_Tarija.xlsx
@@ -8,15 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\schools\colegios\EXTRAIDOS CON PYTHON\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C2504A3-0196-4004-9340-3AF5B841E00C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25977912-EB9F-4FBC-873A-A2AC4FFA7635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -11775,7 +11786,38 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -12074,8 +12116,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:K981"/>
+  <dimension ref="A1:K985"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="18.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -41637,7 +41682,33 @@
         <v>312</v>
       </c>
     </row>
+    <row r="983" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E983">
+        <f>COUNTIF(E1:E981,"Abierta")</f>
+        <v>888</v>
+      </c>
+    </row>
+    <row r="984" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E984">
+        <f>COUNTIF(E1:E981,"Cerrada")</f>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="985" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E985">
+        <f>SUM(E983:E984)</f>
+        <v>978</v>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="E1:E981">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+      <formula>"Cerrada"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"Abierta"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>